--- a/SKU.xlsx
+++ b/SKU.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ข้อมูลในเครื่อง\D - ดาวน์โหลด\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kittiwin\Desktop\web สรุปยอด\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C629A14-1029-46F0-B5D8-0F6D09D1ACDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C8DD71-1D44-4F56-8D50-C491AEC7B72C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12100,7 +12100,7 @@
         <v>683</v>
       </c>
       <c r="F273" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G273" s="3">
         <v>3</v>
